--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7DAF94-927A-40EF-9D0F-F5C8288C5EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FAAE43-1E83-4CA7-A757-F6FC6105ACBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -228,6 +228,15 @@
   <si>
     <t>Tired off due to hectic Schedule.</t>
   </si>
+  <si>
+    <t>Bad</t>
+  </si>
+  <si>
+    <t>Due to some Unfortunate circumstances could'nt attend college</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
 </sst>
 </file>
 
@@ -392,32 +401,20 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -897,74 +894,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
-      <c r="N1" s="14"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16"/>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="17">
         <v>12609633</v>
       </c>
-      <c r="G2" s="15"/>
+      <c r="G2" s="17"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="F3" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="15"/>
+      <c r="G3" s="17"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
+      <c r="H4" s="15"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="15"/>
     </row>
     <row r="5" spans="1:14" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1135,16 +1132,16 @@
         <f t="shared" si="1"/>
         <v>655</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K8" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L8" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M8" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N8" s="14" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1181,16 +1178,16 @@
         <f t="shared" si="1"/>
         <v>562</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K9" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L9" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M9" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N9" s="14" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1227,37 +1224,64 @@
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K10" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L10" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N10" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10" t="str">
+    <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
+        <v>46221</v>
+      </c>
+      <c r="B11" s="9">
+        <v>400</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0</v>
+      </c>
+      <c r="D11" s="9">
+        <v>30</v>
+      </c>
+      <c r="E11" s="9">
+        <v>45</v>
+      </c>
+      <c r="F11" s="9">
+        <v>0</v>
+      </c>
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
+        <v>200</v>
+      </c>
+      <c r="I11" s="10">
+        <f t="shared" si="0"/>
+        <v>675</v>
+      </c>
+      <c r="J11" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="11"/>
-      <c r="N11" s="12"/>
+        <v>765</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="12" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
@@ -9846,16 +9870,16 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K10 K12:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L10 L12:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FAAE43-1E83-4CA7-A757-F6FC6105ACBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A481E647-0B5A-4744-975B-5E372CB18339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -237,6 +237,12 @@
   <si>
     <t>Low</t>
   </si>
+  <si>
+    <t>Feeling bad for situations</t>
+  </si>
+  <si>
+    <t>Busy in rituals</t>
+  </si>
 </sst>
 </file>
 
@@ -409,7 +415,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1284,51 +1292,101 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10" t="str">
+      <c r="A12" s="8">
+        <v>46222</v>
+      </c>
+      <c r="B12" s="9">
+        <v>150</v>
+      </c>
+      <c r="C12" s="9">
+        <v>30</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>40</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>150</v>
+      </c>
+      <c r="I12" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="10" t="str">
+        <v>370</v>
+      </c>
+      <c r="J12" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="12"/>
+        <v>1070</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N12" s="12" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10" t="str">
+      <c r="A13" s="8">
+        <v>46223</v>
+      </c>
+      <c r="B13" s="9">
+        <v>420</v>
+      </c>
+      <c r="C13" s="9">
+        <v>30</v>
+      </c>
+      <c r="D13" s="9">
+        <v>60</v>
+      </c>
+      <c r="E13" s="9">
+        <v>40</v>
+      </c>
+      <c r="F13" s="9">
+        <v>0</v>
+      </c>
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
+        <v>105</v>
+      </c>
+      <c r="I13" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="10" t="str">
+        <v>655</v>
+      </c>
+      <c r="J13" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="12"/>
+        <v>785</v>
+      </c>
+      <c r="K13" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N13" s="12" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8"/>
+      <c r="A14" s="8">
+        <v>46224</v>
+      </c>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A481E647-0B5A-4744-975B-5E372CB18339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E37BB5F-7AAE-4076-BF8A-C99E6731AF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -242,6 +242,9 @@
   </si>
   <si>
     <t>Busy in rituals</t>
+  </si>
+  <si>
+    <t>Fifth day of not attending college</t>
   </si>
 </sst>
 </file>
@@ -1383,29 +1386,51 @@
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
         <v>46224</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10" t="str">
+      <c r="B14" s="9">
+        <v>270</v>
+      </c>
+      <c r="C14" s="9">
+        <v>10</v>
+      </c>
+      <c r="D14" s="9">
+        <v>120</v>
+      </c>
+      <c r="E14" s="9">
+        <v>60</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>55</v>
+      </c>
+      <c r="I14" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="10" t="str">
+        <v>515</v>
+      </c>
+      <c r="J14" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="12"/>
+        <v>925</v>
+      </c>
+      <c r="K14" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N14" s="12" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E37BB5F-7AAE-4076-BF8A-C99E6731AF5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AC4530-8329-4136-9140-B1BF8421BE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>Fifth day of not attending college</t>
+  </si>
+  <si>
+    <t>Boredom</t>
   </si>
 </sst>
 </file>
@@ -1433,26 +1436,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="9"/>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10" t="str">
+      <c r="A15" s="8">
+        <v>46225</v>
+      </c>
+      <c r="B15" s="9">
+        <v>300</v>
+      </c>
+      <c r="C15" s="9">
+        <v>15</v>
+      </c>
+      <c r="D15" s="9">
+        <v>125</v>
+      </c>
+      <c r="E15" s="9">
+        <v>50</v>
+      </c>
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="9">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9">
+        <v>60</v>
+      </c>
+      <c r="I15" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="10" t="str">
+        <v>550</v>
+      </c>
+      <c r="J15" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="12"/>
+        <v>890</v>
+      </c>
+      <c r="K15" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="N15" s="12" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AC4530-8329-4136-9140-B1BF8421BE89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10F6F08-1AE1-4C47-815C-333ED83237CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>Boredom</t>
+  </si>
+  <si>
+    <t>Exploring something new</t>
   </si>
 </sst>
 </file>
@@ -1482,26 +1485,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="9"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10" t="str">
+      <c r="A16" s="8">
+        <v>46226</v>
+      </c>
+      <c r="B16" s="9">
+        <v>360</v>
+      </c>
+      <c r="C16" s="9">
+        <v>30</v>
+      </c>
+      <c r="D16" s="9">
+        <v>120</v>
+      </c>
+      <c r="E16" s="9">
+        <v>60</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>190</v>
+      </c>
+      <c r="I16" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="10" t="str">
+        <v>760</v>
+      </c>
+      <c r="J16" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="12"/>
+        <v>680</v>
+      </c>
+      <c r="K16" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N16" s="12" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10F6F08-1AE1-4C47-815C-333ED83237CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E3F893-AF45-4A87-B3F0-1BFA8DFFF6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>Exploring something new</t>
+  </si>
+  <si>
+    <t>Tired off thinking bout college and collegues.</t>
   </si>
 </sst>
 </file>
@@ -1478,7 +1481,7 @@
         <v>50</v>
       </c>
       <c r="M15" s="11" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="N15" s="12" t="s">
         <v>70</v>
@@ -1530,27 +1533,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10" t="str">
+    <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
+        <v>46227</v>
+      </c>
+      <c r="B17" s="9">
+        <v>420</v>
+      </c>
+      <c r="C17" s="9">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
+        <v>155</v>
+      </c>
+      <c r="E17" s="9">
+        <v>30</v>
+      </c>
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="9">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9">
+        <v>60</v>
+      </c>
+      <c r="I17" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="10" t="str">
+        <v>665</v>
+      </c>
+      <c r="J17" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="12"/>
+        <v>775</v>
+      </c>
+      <c r="K17" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N17" s="12" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E3F893-AF45-4A87-B3F0-1BFA8DFFF6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8080EF-C5CC-4C7D-BAD4-0A6A44FA9DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>Tired off thinking bout college and collegues.</t>
+  </si>
+  <si>
+    <t>Missing new Peers</t>
+  </si>
+  <si>
+    <t>Keeping high as possible as possible</t>
+  </si>
+  <si>
+    <t>Git Add, Commit and Push</t>
   </si>
 </sst>
 </file>
@@ -1580,70 +1589,142 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10" t="str">
+      <c r="A18" s="8">
+        <v>46228</v>
+      </c>
+      <c r="B18" s="9">
+        <v>400</v>
+      </c>
+      <c r="C18" s="9">
+        <v>20</v>
+      </c>
+      <c r="D18" s="9">
+        <v>120</v>
+      </c>
+      <c r="E18" s="9">
+        <v>30</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>80</v>
+      </c>
+      <c r="I18" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="10" t="str">
+        <v>650</v>
+      </c>
+      <c r="J18" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="12"/>
+        <v>790</v>
+      </c>
+      <c r="K18" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N18" s="12" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10" t="str">
+      <c r="A19" s="8">
+        <v>46229</v>
+      </c>
+      <c r="B19" s="9">
+        <v>360</v>
+      </c>
+      <c r="C19" s="9">
+        <v>20</v>
+      </c>
+      <c r="D19" s="9">
+        <v>150</v>
+      </c>
+      <c r="E19" s="9">
+        <v>45</v>
+      </c>
+      <c r="F19" s="9">
+        <v>0</v>
+      </c>
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
+        <v>100</v>
+      </c>
+      <c r="I19" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="10" t="str">
+        <v>675</v>
+      </c>
+      <c r="J19" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="10" t="str">
+        <v>765</v>
+      </c>
+      <c r="K19" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N19" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
+        <v>46230</v>
+      </c>
+      <c r="B20" s="9">
+        <v>240</v>
+      </c>
+      <c r="C20" s="9">
+        <v>30</v>
+      </c>
+      <c r="D20" s="9">
+        <v>120</v>
+      </c>
+      <c r="E20" s="9">
+        <v>30</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>190</v>
+      </c>
+      <c r="I20" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="10" t="str">
+        <v>610</v>
+      </c>
+      <c r="J20" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="12"/>
+        <v>830</v>
+      </c>
+      <c r="K20" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L20" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N20" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8080EF-C5CC-4C7D-BAD4-0A6A44FA9DB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A08D73-ADD4-48F2-943B-F01035614E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -263,6 +263,9 @@
   </si>
   <si>
     <t>Git Add, Commit and Push</t>
+  </si>
+  <si>
+    <t>Explored superficiality</t>
   </si>
 </sst>
 </file>
@@ -1727,26 +1730,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="10" t="str">
+      <c r="A21" s="8">
+        <v>46231</v>
+      </c>
+      <c r="B21" s="9">
+        <v>300</v>
+      </c>
+      <c r="C21" s="9">
+        <v>30</v>
+      </c>
+      <c r="D21" s="9">
+        <v>120</v>
+      </c>
+      <c r="E21" s="9">
+        <v>0</v>
+      </c>
+      <c r="F21" s="9">
+        <v>0</v>
+      </c>
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
+        <v>180</v>
+      </c>
+      <c r="I21" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="10" t="str">
+        <v>630</v>
+      </c>
+      <c r="J21" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="11"/>
-      <c r="N21" s="12"/>
+        <v>810</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N21" s="12" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A08D73-ADD4-48F2-943B-F01035614E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7D4166-6377-4736-9ACF-FD68BFF68252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -266,6 +266,12 @@
   </si>
   <si>
     <t>Explored superficiality</t>
+  </si>
+  <si>
+    <t>Penultimate day of Ritual</t>
+  </si>
+  <si>
+    <t>The Last Day of Rites and the day to learn other than prior base.</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1231,7 @@
     </row>
     <row r="10" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46220</v>
+        <v>46251</v>
       </c>
       <c r="B10" s="9">
         <v>360</v>
@@ -1271,7 +1277,7 @@
     </row>
     <row r="11" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46221</v>
+        <v>46252</v>
       </c>
       <c r="B11" s="9">
         <v>400</v>
@@ -1317,7 +1323,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46222</v>
+        <v>46253</v>
       </c>
       <c r="B12" s="9">
         <v>150</v>
@@ -1363,7 +1369,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46223</v>
+        <v>46254</v>
       </c>
       <c r="B13" s="9">
         <v>420</v>
@@ -1409,7 +1415,7 @@
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46224</v>
+        <v>46255</v>
       </c>
       <c r="B14" s="9">
         <v>270</v>
@@ -1455,7 +1461,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46225</v>
+        <v>46256</v>
       </c>
       <c r="B15" s="9">
         <v>300</v>
@@ -1501,7 +1507,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46226</v>
+        <v>46257</v>
       </c>
       <c r="B16" s="9">
         <v>360</v>
@@ -1547,7 +1553,7 @@
     </row>
     <row r="17" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46227</v>
+        <v>46258</v>
       </c>
       <c r="B17" s="9">
         <v>420</v>
@@ -1593,7 +1599,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46228</v>
+        <v>46259</v>
       </c>
       <c r="B18" s="9">
         <v>400</v>
@@ -1639,7 +1645,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46229</v>
+        <v>46260</v>
       </c>
       <c r="B19" s="9">
         <v>360</v>
@@ -1685,7 +1691,7 @@
     </row>
     <row r="20" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46230</v>
+        <v>46261</v>
       </c>
       <c r="B20" s="9">
         <v>240</v>
@@ -1731,7 +1737,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>46231</v>
+        <v>46262</v>
       </c>
       <c r="B21" s="9">
         <v>300</v>
@@ -1776,48 +1782,96 @@
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="10" t="str">
+      <c r="A22" s="8">
+        <v>46263</v>
+      </c>
+      <c r="B22" s="9">
+        <v>255</v>
+      </c>
+      <c r="C22" s="9">
+        <v>30</v>
+      </c>
+      <c r="D22" s="9">
+        <v>150</v>
+      </c>
+      <c r="E22" s="9">
+        <v>20</v>
+      </c>
+      <c r="F22" s="9">
+        <v>0</v>
+      </c>
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
+        <v>210</v>
+      </c>
+      <c r="I22" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="10" t="str">
+        <v>665</v>
+      </c>
+      <c r="J22" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="12"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="10" t="str">
+        <v>775</v>
+      </c>
+      <c r="K22" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L22" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M22" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N22" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
+        <v>46264</v>
+      </c>
+      <c r="B23" s="9">
+        <v>360</v>
+      </c>
+      <c r="C23" s="9">
+        <v>15</v>
+      </c>
+      <c r="D23" s="9">
+        <v>60</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0</v>
+      </c>
+      <c r="F23" s="9">
+        <v>0</v>
+      </c>
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
+        <v>180</v>
+      </c>
+      <c r="I23" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="10" t="str">
+        <v>615</v>
+      </c>
+      <c r="J23" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="11"/>
-      <c r="N23" s="12"/>
+        <v>825</v>
+      </c>
+      <c r="K23" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L23" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M23" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N23" s="12" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7D4166-6377-4736-9ACF-FD68BFF68252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F0CABE-91C6-47BE-916A-E59B065624EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -272,6 +272,15 @@
   </si>
   <si>
     <t>The Last Day of Rites and the day to learn other than prior base.</t>
+  </si>
+  <si>
+    <t>You sleep very well after a responsibility is completed</t>
+  </si>
+  <si>
+    <t>Could not catch my early morning train</t>
+  </si>
+  <si>
+    <t>Finally got a bus to LPU</t>
   </si>
 </sst>
 </file>
@@ -1873,71 +1882,143 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="10" t="str">
+    <row r="24" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B24" s="9">
+        <v>480</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0</v>
+      </c>
+      <c r="D24" s="9">
+        <v>60</v>
+      </c>
+      <c r="E24" s="9">
+        <v>60</v>
+      </c>
+      <c r="F24" s="9">
+        <v>0</v>
+      </c>
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
+        <v>155</v>
+      </c>
+      <c r="I24" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="10" t="str">
+        <v>755</v>
+      </c>
+      <c r="J24" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="11"/>
-      <c r="N24" s="12"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="10" t="str">
+        <v>685</v>
+      </c>
+      <c r="K24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L24" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M24" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="N24" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
+        <v>46266</v>
+      </c>
+      <c r="B25" s="9">
+        <v>360</v>
+      </c>
+      <c r="C25" s="9">
+        <v>30</v>
+      </c>
+      <c r="D25" s="9">
+        <v>150</v>
+      </c>
+      <c r="E25" s="9">
+        <v>60</v>
+      </c>
+      <c r="F25" s="9">
+        <v>0</v>
+      </c>
+      <c r="G25" s="9">
+        <v>0</v>
+      </c>
+      <c r="H25" s="9">
+        <v>200</v>
+      </c>
+      <c r="I25" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="10" t="str">
+        <v>800</v>
+      </c>
+      <c r="J25" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="12"/>
+        <v>640</v>
+      </c>
+      <c r="K25" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="L25" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M25" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N25" s="12" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="10" t="str">
+      <c r="A26" s="8">
+        <v>46267</v>
+      </c>
+      <c r="B26" s="9">
+        <v>380</v>
+      </c>
+      <c r="C26" s="9">
+        <v>30</v>
+      </c>
+      <c r="D26" s="9">
+        <v>220</v>
+      </c>
+      <c r="E26" s="9">
+        <v>40</v>
+      </c>
+      <c r="F26" s="9">
+        <v>0</v>
+      </c>
+      <c r="G26" s="9">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
+        <v>50</v>
+      </c>
+      <c r="I26" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="10" t="str">
+        <v>720</v>
+      </c>
+      <c r="J26" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="11"/>
-      <c r="N26" s="12"/>
+        <v>720</v>
+      </c>
+      <c r="K26" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L26" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M26" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N26" s="12" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F0CABE-91C6-47BE-916A-E59B065624EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED5BEC4-4C18-40E0-A5CC-5FA92C14069B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -281,6 +281,9 @@
   </si>
   <si>
     <t>Finally got a bus to LPU</t>
+  </si>
+  <si>
+    <t>First day at college after a long cut-off</t>
   </si>
 </sst>
 </file>
@@ -1056,7 +1059,7 @@
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46216</v>
+        <v>46247</v>
       </c>
       <c r="B6" s="9">
         <v>360</v>
@@ -1102,7 +1105,7 @@
     </row>
     <row r="7" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>46217</v>
+        <v>46248</v>
       </c>
       <c r="B7" s="9">
         <v>360</v>
@@ -1148,7 +1151,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46218</v>
+        <v>46249</v>
       </c>
       <c r="B8" s="9">
         <v>480</v>
@@ -1194,7 +1197,7 @@
     </row>
     <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46219</v>
+        <v>46250</v>
       </c>
       <c r="B9" s="9">
         <v>420</v>
@@ -2020,27 +2023,49 @@
         <v>81</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8"/>
+    <row r="27" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
+        <v>46268</v>
+      </c>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="10" t="str">
+      <c r="C27" s="9">
+        <v>375</v>
+      </c>
+      <c r="D27" s="9">
+        <v>60</v>
+      </c>
+      <c r="E27" s="9">
+        <v>0</v>
+      </c>
+      <c r="F27" s="9">
+        <v>150</v>
+      </c>
+      <c r="G27" s="9">
+        <v>3</v>
+      </c>
+      <c r="H27" s="9">
+        <v>60</v>
+      </c>
+      <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J27" s="10" t="str">
+        <v>645</v>
+      </c>
+      <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="12"/>
+        <v>795</v>
+      </c>
+      <c r="K27" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L27" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M27" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N27" s="12" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED5BEC4-4C18-40E0-A5CC-5FA92C14069B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5E61AA-D095-494B-B3C2-1FBA661A59E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>First day at college after a long cut-off</t>
+  </si>
+  <si>
+    <t>Weekend are so satisfactory</t>
   </si>
 </sst>
 </file>
@@ -2027,9 +2030,11 @@
       <c r="A27" s="8">
         <v>46268</v>
       </c>
-      <c r="B27" s="9"/>
+      <c r="B27" s="9">
+        <v>375</v>
+      </c>
       <c r="C27" s="9">
-        <v>375</v>
+        <v>30</v>
       </c>
       <c r="D27" s="9">
         <v>60</v>
@@ -2038,21 +2043,21 @@
         <v>0</v>
       </c>
       <c r="F27" s="9">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G27" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="9">
         <v>60</v>
       </c>
       <c r="I27" s="10">
         <f t="shared" si="0"/>
-        <v>645</v>
+        <v>575</v>
       </c>
       <c r="J27" s="10">
         <f t="shared" si="1"/>
-        <v>795</v>
+        <v>865</v>
       </c>
       <c r="K27" s="11" t="s">
         <v>49</v>
@@ -2068,26 +2073,50 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="10" t="str">
+      <c r="A28" s="8">
+        <v>46269</v>
+      </c>
+      <c r="B28" s="9">
+        <v>360</v>
+      </c>
+      <c r="C28" s="9">
+        <v>30</v>
+      </c>
+      <c r="D28" s="9">
+        <v>180</v>
+      </c>
+      <c r="E28" s="9">
+        <v>39</v>
+      </c>
+      <c r="F28" s="9">
+        <v>150</v>
+      </c>
+      <c r="G28" s="9">
+        <v>3</v>
+      </c>
+      <c r="H28" s="9">
+        <v>180</v>
+      </c>
+      <c r="I28" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J28" s="10" t="str">
+        <v>939</v>
+      </c>
+      <c r="J28" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="11"/>
-      <c r="N28" s="12"/>
+        <v>501</v>
+      </c>
+      <c r="K28" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L28" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M28" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N28" s="12" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B5E61AA-D095-494B-B3C2-1FBA661A59E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BD8B2F-8688-4B2D-BFFE-AAB41C2F1A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -286,7 +286,7 @@
     <t>First day at college after a long cut-off</t>
   </si>
   <si>
-    <t>Weekend are so satisfactory</t>
+    <t>Weekends are so satisfactory</t>
   </si>
 </sst>
 </file>
@@ -2072,7 +2072,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>46269</v>
       </c>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BD8B2F-8688-4B2D-BFFE-AAB41C2F1A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD0C6F3-1EF7-4709-AA0D-BADDA2672169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -287,6 +287,9 @@
   </si>
   <si>
     <t>Weekends are so satisfactory</t>
+  </si>
+  <si>
+    <t>Day before first ever CA in LPU, enjoying to learn for the same.</t>
   </si>
 </sst>
 </file>
@@ -1198,7 +1201,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
         <v>46250</v>
       </c>
@@ -2072,7 +2075,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>46269</v>
       </c>
@@ -2119,7 +2122,9 @@
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8"/>
+      <c r="A29" s="8">
+        <v>46270</v>
+      </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="D29" s="9"/>
@@ -2140,27 +2145,51 @@
       <c r="M29" s="11"/>
       <c r="N29" s="12"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="10" t="str">
+    <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
+        <v>46271</v>
+      </c>
+      <c r="B30" s="9">
+        <v>400</v>
+      </c>
+      <c r="C30" s="9">
+        <v>20</v>
+      </c>
+      <c r="D30" s="9">
+        <v>240</v>
+      </c>
+      <c r="E30" s="9">
+        <v>30</v>
+      </c>
+      <c r="F30" s="9">
+        <v>0</v>
+      </c>
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
+        <v>30</v>
+      </c>
+      <c r="I30" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J30" s="10" t="str">
+        <v>720</v>
+      </c>
+      <c r="J30" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="11"/>
-      <c r="N30" s="12"/>
+        <v>720</v>
+      </c>
+      <c r="K30" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L30" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M30" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N30" s="12" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8"/>

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD0C6F3-1EF7-4709-AA0D-BADDA2672169}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9352EB8A-49F3-4B81-ACB1-1D2A69DF1D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Day before first ever CA in LPU, enjoying to learn for the same.</t>
+  </si>
+  <si>
+    <t>Completing all stuff, collected for the weekend.</t>
   </si>
 </sst>
 </file>
@@ -2075,7 +2078,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
         <v>46269</v>
       </c>
@@ -2121,29 +2124,51 @@
         <v>83</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>46270</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="10" t="str">
+      <c r="B29" s="9">
+        <v>390</v>
+      </c>
+      <c r="C29" s="9">
+        <v>0</v>
+      </c>
+      <c r="D29" s="9">
+        <v>60</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0</v>
+      </c>
+      <c r="F29" s="9">
+        <v>0</v>
+      </c>
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
+        <v>230</v>
+      </c>
+      <c r="I29" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J29" s="10" t="str">
+        <v>680</v>
+      </c>
+      <c r="J29" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="12"/>
+        <v>760</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N29" s="12" t="s">
+        <v>85</v>
+      </c>
     </row>
     <row r="30" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A30" s="8">

--- a/12609633.xlsx
+++ b/12609633.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\singh\Documents\my-data-my-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9352EB8A-49F3-4B81-ACB1-1D2A69DF1D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A23E5E-F0E6-4882-BD83-583B90D3A2C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -293,6 +293,9 @@
   </si>
   <si>
     <t>Completing all stuff, collected for the weekend.</t>
+  </si>
+  <si>
+    <t>First CA done, subject - DBMS.</t>
   </si>
 </sst>
 </file>
@@ -2216,30 +2219,56 @@
         <v>84</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="10" t="str">
+    <row r="31" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B31" s="9">
+        <v>240</v>
+      </c>
+      <c r="C31" s="9">
+        <v>40</v>
+      </c>
+      <c r="D31" s="9">
+        <v>260</v>
+      </c>
+      <c r="E31" s="9">
+        <v>50</v>
+      </c>
+      <c r="F31" s="9">
+        <v>350</v>
+      </c>
+      <c r="G31" s="9">
+        <v>7</v>
+      </c>
+      <c r="H31" s="9">
+        <v>100</v>
+      </c>
+      <c r="I31" s="10">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J31" s="10" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J31" s="10">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M31" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N31" s="12" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8"/>
+      <c r="A32" s="8">
+        <v>46273</v>
+      </c>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
